--- a/data/trans_orig/P70C3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023</t>
+          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>32165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64999</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>63072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82570</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120617</t>
+          <t>122894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>61521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>31949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1295,97 +1295,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3610</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178872</t>
+          <t>180420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226404</t>
+          <t>225385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191914</t>
+          <t>193327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291014</t>
+          <t>294124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389964</t>
+          <t>390399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507757</t>
+          <t>507986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>49322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>84752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>37998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105282</t>
+          <t>104611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104153</t>
+          <t>101986</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176605</t>
+          <t>172876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>71271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61698</t>
+          <t>60832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>40523</t>
+          <t>42908</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238462</t>
+          <t>238101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>283432</t>
+          <t>283693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161064</t>
+          <t>159643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190798</t>
+          <t>190884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>412492</t>
+          <t>411106</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>464769</t>
+          <t>463037</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114788</t>
+          <t>112627</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79971</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107145</t>
+          <t>107032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166638</t>
+          <t>168005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211611</t>
+          <t>211761</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>34533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61661</t>
+          <t>62939</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60275</t>
+          <t>60552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92090</t>
+          <t>92171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27567</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53441</t>
+          <t>53370</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84716</t>
+          <t>85190</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>421473</t>
+          <t>425822</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>659540</t>
+          <t>665191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>243206</t>
+          <t>243616</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>312459</t>
+          <t>311580</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>688677</t>
+          <t>682335</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>995543</t>
+          <t>979184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51632</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>192427</t>
+          <t>187947</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72673</t>
+          <t>73663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111667</t>
+          <t>111717</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116954</t>
+          <t>122574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285440</t>
+          <t>288303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46006</t>
+          <t>43581</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30254</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>87130</t>
+          <t>84267</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>50326</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28653</t>
+          <t>28639</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75888</t>
+          <t>76635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>53584</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39045</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>47812</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>141542</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>174445</t>
+          <t>174351</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>97065</t>
+          <t>98215</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>117988</t>
+          <t>118379</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>248038</t>
+          <t>247985</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>285730</t>
+          <t>285743</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>65176</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>93233</t>
+          <t>93883</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>47322</t>
+          <t>47223</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>65749</t>
+          <t>65399</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>119637</t>
+          <t>120690</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>151843</t>
+          <t>150976</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55883</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>31435</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27644</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>339</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -5157,97 +5157,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>994</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>3579</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5270,97 +5270,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>3424</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>3451</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5500,97 +5500,97 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="W46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -5613,97 +5613,97 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="W47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5726,97 +5726,97 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5839,97 +5839,97 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5952,97 +5952,97 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6065,97 +6065,97 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1100609</t>
+          <t>1096775</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1464224</t>
+          <t>1490859</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>787801</t>
+          <t>793114</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>948443</t>
+          <t>932006</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1918805</t>
+          <t>1914075</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2339860</t>
+          <t>2376111</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>246621</t>
+          <t>246584</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>459577</t>
+          <t>459871</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>293351</t>
+          <t>295082</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>384547</t>
+          <t>382589</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>588144</t>
+          <t>570082</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>826312</t>
+          <t>827734</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>97115</t>
+          <t>94785</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>176428</t>
+          <t>176221</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>87040</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>128919</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>199122</t>
+          <t>190239</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>289608</t>
+          <t>286151</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>154573</t>
+          <t>152722</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>106799</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>167488</t>
+          <t>159040</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>245454</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>37659</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>38448</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>88447</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>139554</t>
+          <t>141313</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>77691</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>56805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64626</t>
+          <t>72459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42172</t>
+          <t>46996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63072</t>
+          <t>71419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>102436</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84481</t>
+          <t>97082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122894</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>43945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>51971</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29225</t>
+          <t>35543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61521</t>
+          <t>69941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>203357</t>
+          <t>221849</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180420</t>
+          <t>194384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225385</t>
+          <t>247965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>230174</t>
+          <t>183394</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193327</t>
+          <t>165771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>294124</t>
+          <t>201176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>433530</t>
+          <t>405243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390399</t>
+          <t>375137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507986</t>
+          <t>435696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>83481</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49322</t>
+          <t>64326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84752</t>
+          <t>104729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78961</t>
+          <t>86348</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37998</t>
+          <t>70148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104611</t>
+          <t>101388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>169829</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101986</t>
+          <t>146289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172876</t>
+          <t>195289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>36814</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>59383</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34211</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71271</t>
+          <t>80234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26564</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60832</t>
+          <t>62629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1972,22 +1972,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>260772</t>
+          <t>304143</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238101</t>
+          <t>279301</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>283693</t>
+          <t>328086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>175769</t>
+          <t>199224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159643</t>
+          <t>181082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190884</t>
+          <t>215271</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>436541</t>
+          <t>503366</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>411106</t>
+          <t>471102</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>463037</t>
+          <t>531320</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94755</t>
+          <t>114001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>93999</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112627</t>
+          <t>135311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93529</t>
+          <t>105227</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>91073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107032</t>
+          <t>121484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>188284</t>
+          <t>219228</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168005</t>
+          <t>195265</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211761</t>
+          <t>244838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>56636</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62939</t>
+          <t>70950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>27739</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20699</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>75435</t>
+          <t>87479</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60552</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92171</t>
+          <t>105797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>57678</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>31927</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>42066</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>67731</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>57838</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85190</t>
+          <t>93459</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>30669</t>
+          <t>34919</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42956</t>
+          <t>48915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>461983</t>
+          <t>538246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>461983</t>
+          <t>538246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>461983</t>
+          <t>538246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>350218</t>
+          <t>396484</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>350218</t>
+          <t>396484</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>350218</t>
+          <t>396484</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>812201</t>
+          <t>934730</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>812201</t>
+          <t>934730</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>812201</t>
+          <t>934730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>536807</t>
+          <t>322157</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>425822</t>
+          <t>298594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>665191</t>
+          <t>345091</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>265385</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>243616</t>
+          <t>235742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>311580</t>
+          <t>268545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>802192</t>
+          <t>575111</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>682335</t>
+          <t>545813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>979184</t>
+          <t>604805</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>121893</t>
+          <t>131757</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>114558</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187947</t>
+          <t>151282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>96370</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73663</t>
+          <t>94128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111717</t>
+          <t>122355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>218264</t>
+          <t>239143</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122574</t>
+          <t>214328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288303</t>
+          <t>264090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>38413</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36859</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48195</t>
+          <t>49704</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>67008</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>54093</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>83258</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>58816</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>46774</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76635</t>
+          <t>72743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>40007</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35762</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>32821</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>453598</t>
+          <t>455690</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>453598</t>
+          <t>455690</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>453598</t>
+          <t>455690</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1202022</t>
+          <t>1002516</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1202022</t>
+          <t>1002516</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1202022</t>
+          <t>1002516</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>178271</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>141542</t>
+          <t>160518</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>174351</t>
+          <t>194769</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>107874</t>
+          <t>123333</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>98215</t>
+          <t>111061</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>118379</t>
+          <t>134685</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>266516</t>
+          <t>301604</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>247985</t>
+          <t>281943</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>285743</t>
+          <t>322793</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>78998</t>
+          <t>84581</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>65092</t>
+          <t>71031</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>93883</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>56299</t>
+          <t>60933</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>50755</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>65399</t>
+          <t>70767</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>135297</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>120690</t>
+          <t>127702</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>150976</t>
+          <t>163544</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34808</t>
+          <t>36834</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>34512</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>53915</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24854</t>
+          <t>26551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4470,67 +4470,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>4371</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>8076</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>4048</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>1682</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>7845</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>508071</t>
+          <t>562246</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>508071</t>
+          <t>562246</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>508071</t>
+          <t>562246</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>595</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1220717</t>
+          <t>1096283</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1096775</t>
+          <t>1043277</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1490859</t>
+          <t>1143020</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>841435</t>
+          <t>828102</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>793114</t>
+          <t>794624</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>932006</t>
+          <t>863214</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2062152</t>
+          <t>1924384</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1914075</t>
+          <t>1855821</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2376111</t>
+          <t>1985658</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>390512</t>
+          <t>447746</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>246584</t>
+          <t>410939</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>459871</t>
+          <t>489286</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>349728</t>
+          <t>389018</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>295082</t>
+          <t>359376</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>382589</t>
+          <t>422537</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>740240</t>
+          <t>836764</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>570082</t>
+          <t>785447</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>827734</t>
+          <t>885705</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>133456</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>176221</t>
+          <t>188963</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>100326</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>125268</t>
+          <t>137841</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>248813</t>
+          <t>277500</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>190239</t>
+          <t>245777</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>286151</t>
+          <t>311375</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>129543</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>106890</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>152722</t>
+          <t>156416</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>80090</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>106799</t>
+          <t>114341</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>197936</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>245454</t>
+          <t>260345</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>114840</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>88447</t>
+          <t>108059</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>58613</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>76991</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
